--- a/templates/ERC000043/metadata_template_ERC000043.xlsx
+++ b/templates/ERC000043/metadata_template_ERC000043.xlsx
@@ -19,7 +19,7 @@
   <definedNames>
     <definedName name="fileformat">'cv_run'!$D$1:$D$24</definedName>
     <definedName name="geographiclocationcountryandorsea">'cv_sample'!$O$1:$O$289</definedName>
-    <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$85</definedName>
+    <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$87</definedName>
     <definedName name="libraryselection">'cv_experiment'!$I$1:$I$31</definedName>
     <definedName name="librarysource">'cv_experiment'!$H$1:$H$9</definedName>
     <definedName name="librarystrategy">'cv_experiment'!$G$1:$G$41</definedName>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="605" uniqueCount="597">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="607" uniqueCount="599">
   <si>
     <t>alias</t>
   </si>
@@ -555,6 +555,9 @@
     <t>DNBSEQ-G50</t>
   </si>
   <si>
+    <t>DNBSEQ-G800</t>
+  </si>
+  <si>
     <t>DNBSEQ-T10x4RS</t>
   </si>
   <si>
@@ -718,6 +721,9 @@
   </si>
   <si>
     <t>UG 100</t>
+  </si>
+  <si>
+    <t>Vega</t>
   </si>
   <si>
     <t>instrument_model</t>
@@ -2351,7 +2357,7 @@
         <v>143</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="150" customHeight="1">
@@ -2395,7 +2401,7 @@
         <v>144</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
   </sheetData>
@@ -2422,7 +2428,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="G1:N85"/>
+  <dimension ref="G1:N87"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="7:14">
@@ -3141,6 +3147,16 @@
     </row>
     <row r="85" spans="14:14">
       <c r="N85" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="86" spans="14:14">
+      <c r="N86" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="87" spans="14:14">
+      <c r="N87" t="s">
         <v>117</v>
       </c>
     </row>
@@ -3162,27 +3178,27 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
     </row>
   </sheetData>
@@ -3202,122 +3218,122 @@
   <sheetData>
     <row r="1" spans="4:4">
       <c r="D1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="2" spans="4:4">
       <c r="D2" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
     </row>
     <row r="3" spans="4:4">
       <c r="D3" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="4" spans="4:4">
       <c r="D4" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="5" spans="4:4">
       <c r="D5" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="6" spans="4:4">
       <c r="D6" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="7" spans="4:4">
       <c r="D7" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="8" spans="4:4">
       <c r="D8" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="9" spans="4:4">
       <c r="D9" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="10" spans="4:4">
       <c r="D10" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="11" spans="4:4">
       <c r="D11" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="12" spans="4:4">
       <c r="D12" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="13" spans="4:4">
       <c r="D13" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="14" spans="4:4">
       <c r="D14" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="15" spans="4:4">
       <c r="D15" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="16" spans="4:4">
       <c r="D16" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
     </row>
     <row r="17" spans="4:4">
       <c r="D17" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="18" spans="4:4">
       <c r="D18" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
     </row>
     <row r="19" spans="4:4">
       <c r="D19" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="20" spans="4:4">
       <c r="D20" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="21" spans="4:4">
       <c r="D21" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="22" spans="4:4">
       <c r="D22" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
     </row>
     <row r="23" spans="4:4">
       <c r="D23" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="24" spans="4:4">
       <c r="D24" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
   </sheetData>
@@ -3341,144 +3357,144 @@
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
     </row>
     <row r="2" spans="1:24" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="U2" s="2" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="V2" s="2" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="W2" s="2" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="X2" s="2" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
     </row>
   </sheetData>
@@ -3498,1447 +3514,1447 @@
   <sheetData>
     <row r="1" spans="15:15">
       <c r="O1" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="2" spans="15:15">
       <c r="O2" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="3" spans="15:15">
       <c r="O3" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="4" spans="15:15">
       <c r="O4" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="5" spans="15:15">
       <c r="O5" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="6" spans="15:15">
       <c r="O6" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="7" spans="15:15">
       <c r="O7" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="8" spans="15:15">
       <c r="O8" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="9" spans="15:15">
       <c r="O9" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="10" spans="15:15">
       <c r="O10" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="11" spans="15:15">
       <c r="O11" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="12" spans="15:15">
       <c r="O12" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="13" spans="15:15">
       <c r="O13" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="14" spans="15:15">
       <c r="O14" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="15" spans="15:15">
       <c r="O15" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="16" spans="15:15">
       <c r="O16" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="17" spans="15:15">
       <c r="O17" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="18" spans="15:15">
       <c r="O18" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="19" spans="15:15">
       <c r="O19" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="20" spans="15:15">
       <c r="O20" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="21" spans="15:15">
       <c r="O21" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="22" spans="15:15">
       <c r="O22" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="23" spans="15:15">
       <c r="O23" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="24" spans="15:15">
       <c r="O24" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="25" spans="15:15">
       <c r="O25" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="26" spans="15:15">
       <c r="O26" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="27" spans="15:15">
       <c r="O27" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="28" spans="15:15">
       <c r="O28" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="29" spans="15:15">
       <c r="O29" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="30" spans="15:15">
       <c r="O30" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="31" spans="15:15">
       <c r="O31" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="32" spans="15:15">
       <c r="O32" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="33" spans="15:15">
       <c r="O33" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="34" spans="15:15">
       <c r="O34" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="35" spans="15:15">
       <c r="O35" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="36" spans="15:15">
       <c r="O36" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="37" spans="15:15">
       <c r="O37" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="38" spans="15:15">
       <c r="O38" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="39" spans="15:15">
       <c r="O39" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="40" spans="15:15">
       <c r="O40" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="41" spans="15:15">
       <c r="O41" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="42" spans="15:15">
       <c r="O42" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="43" spans="15:15">
       <c r="O43" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="44" spans="15:15">
       <c r="O44" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="45" spans="15:15">
       <c r="O45" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="46" spans="15:15">
       <c r="O46" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="47" spans="15:15">
       <c r="O47" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="48" spans="15:15">
       <c r="O48" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="49" spans="15:15">
       <c r="O49" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="50" spans="15:15">
       <c r="O50" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="51" spans="15:15">
       <c r="O51" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="52" spans="15:15">
       <c r="O52" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="53" spans="15:15">
       <c r="O53" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="54" spans="15:15">
       <c r="O54" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="55" spans="15:15">
       <c r="O55" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="56" spans="15:15">
       <c r="O56" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="57" spans="15:15">
       <c r="O57" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="58" spans="15:15">
       <c r="O58" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="59" spans="15:15">
       <c r="O59" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="60" spans="15:15">
       <c r="O60" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="61" spans="15:15">
       <c r="O61" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="62" spans="15:15">
       <c r="O62" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="63" spans="15:15">
       <c r="O63" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="64" spans="15:15">
       <c r="O64" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="65" spans="15:15">
       <c r="O65" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="66" spans="15:15">
       <c r="O66" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="67" spans="15:15">
       <c r="O67" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="68" spans="15:15">
       <c r="O68" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="69" spans="15:15">
       <c r="O69" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="70" spans="15:15">
       <c r="O70" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="71" spans="15:15">
       <c r="O71" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="72" spans="15:15">
       <c r="O72" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
     </row>
     <row r="73" spans="15:15">
       <c r="O73" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="74" spans="15:15">
       <c r="O74" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="75" spans="15:15">
       <c r="O75" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="76" spans="15:15">
       <c r="O76" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="77" spans="15:15">
       <c r="O77" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="78" spans="15:15">
       <c r="O78" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="79" spans="15:15">
       <c r="O79" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
     </row>
     <row r="80" spans="15:15">
       <c r="O80" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="81" spans="15:15">
       <c r="O81" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="82" spans="15:15">
       <c r="O82" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="83" spans="15:15">
       <c r="O83" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="84" spans="15:15">
       <c r="O84" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="85" spans="15:15">
       <c r="O85" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="86" spans="15:15">
       <c r="O86" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="87" spans="15:15">
       <c r="O87" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="88" spans="15:15">
       <c r="O88" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="89" spans="15:15">
       <c r="O89" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="90" spans="15:15">
       <c r="O90" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="91" spans="15:15">
       <c r="O91" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="92" spans="15:15">
       <c r="O92" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="93" spans="15:15">
       <c r="O93" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="94" spans="15:15">
       <c r="O94" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="95" spans="15:15">
       <c r="O95" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="96" spans="15:15">
       <c r="O96" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="97" spans="15:15">
       <c r="O97" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="98" spans="15:15">
       <c r="O98" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="99" spans="15:15">
       <c r="O99" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="100" spans="15:15">
       <c r="O100" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="101" spans="15:15">
       <c r="O101" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="102" spans="15:15">
       <c r="O102" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="103" spans="15:15">
       <c r="O103" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="104" spans="15:15">
       <c r="O104" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="105" spans="15:15">
       <c r="O105" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="106" spans="15:15">
       <c r="O106" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="107" spans="15:15">
       <c r="O107" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="108" spans="15:15">
       <c r="O108" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="109" spans="15:15">
       <c r="O109" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="110" spans="15:15">
       <c r="O110" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="111" spans="15:15">
       <c r="O111" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="112" spans="15:15">
       <c r="O112" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="113" spans="15:15">
       <c r="O113" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="114" spans="15:15">
       <c r="O114" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="115" spans="15:15">
       <c r="O115" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="116" spans="15:15">
       <c r="O116" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="117" spans="15:15">
       <c r="O117" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
     </row>
     <row r="118" spans="15:15">
       <c r="O118" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
     <row r="119" spans="15:15">
       <c r="O119" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
     </row>
     <row r="120" spans="15:15">
       <c r="O120" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="121" spans="15:15">
       <c r="O121" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="122" spans="15:15">
       <c r="O122" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="123" spans="15:15">
       <c r="O123" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="124" spans="15:15">
       <c r="O124" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="125" spans="15:15">
       <c r="O125" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="126" spans="15:15">
       <c r="O126" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
     <row r="127" spans="15:15">
       <c r="O127" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="128" spans="15:15">
       <c r="O128" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
     </row>
     <row r="129" spans="15:15">
       <c r="O129" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="130" spans="15:15">
       <c r="O130" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
     </row>
     <row r="131" spans="15:15">
       <c r="O131" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="132" spans="15:15">
       <c r="O132" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="133" spans="15:15">
       <c r="O133" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="134" spans="15:15">
       <c r="O134" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
     </row>
     <row r="135" spans="15:15">
       <c r="O135" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="136" spans="15:15">
       <c r="O136" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
     <row r="137" spans="15:15">
       <c r="O137" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="138" spans="15:15">
       <c r="O138" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="139" spans="15:15">
       <c r="O139" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
     </row>
     <row r="140" spans="15:15">
       <c r="O140" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="141" spans="15:15">
       <c r="O141" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="142" spans="15:15">
       <c r="O142" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
     <row r="143" spans="15:15">
       <c r="O143" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
     </row>
     <row r="144" spans="15:15">
       <c r="O144" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="145" spans="15:15">
       <c r="O145" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="146" spans="15:15">
       <c r="O146" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
     </row>
     <row r="147" spans="15:15">
       <c r="O147" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
     </row>
     <row r="148" spans="15:15">
       <c r="O148" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="149" spans="15:15">
       <c r="O149" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
     </row>
     <row r="150" spans="15:15">
       <c r="O150" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
     <row r="151" spans="15:15">
       <c r="O151" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="152" spans="15:15">
       <c r="O152" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="153" spans="15:15">
       <c r="O153" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="154" spans="15:15">
       <c r="O154" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
     </row>
     <row r="155" spans="15:15">
       <c r="O155" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
     <row r="156" spans="15:15">
       <c r="O156" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
     </row>
     <row r="157" spans="15:15">
       <c r="O157" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
     </row>
     <row r="158" spans="15:15">
       <c r="O158" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="159" spans="15:15">
       <c r="O159" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
     </row>
     <row r="160" spans="15:15">
       <c r="O160" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
     <row r="161" spans="15:15">
       <c r="O161" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="162" spans="15:15">
       <c r="O162" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
     </row>
     <row r="163" spans="15:15">
       <c r="O163" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
     </row>
     <row r="164" spans="15:15">
       <c r="O164" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="165" spans="15:15">
       <c r="O165" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
     </row>
     <row r="166" spans="15:15">
       <c r="O166" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
     </row>
     <row r="167" spans="15:15">
       <c r="O167" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="168" spans="15:15">
       <c r="O168" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
     </row>
     <row r="169" spans="15:15">
       <c r="O169" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
     </row>
     <row r="170" spans="15:15">
       <c r="O170" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
     </row>
     <row r="171" spans="15:15">
       <c r="O171" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
     </row>
     <row r="172" spans="15:15">
       <c r="O172" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="173" spans="15:15">
       <c r="O173" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
     </row>
     <row r="174" spans="15:15">
       <c r="O174" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="175" spans="15:15">
       <c r="O175" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
     </row>
     <row r="176" spans="15:15">
       <c r="O176" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
     </row>
     <row r="177" spans="15:15">
       <c r="O177" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="178" spans="15:15">
       <c r="O178" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="179" spans="15:15">
       <c r="O179" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
     </row>
     <row r="180" spans="15:15">
       <c r="O180" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="181" spans="15:15">
       <c r="O181" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
     </row>
     <row r="182" spans="15:15">
       <c r="O182" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
     </row>
     <row r="183" spans="15:15">
       <c r="O183" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="184" spans="15:15">
       <c r="O184" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="185" spans="15:15">
       <c r="O185" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="186" spans="15:15">
       <c r="O186" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
     </row>
     <row r="187" spans="15:15">
       <c r="O187" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
     <row r="188" spans="15:15">
       <c r="O188" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
     </row>
     <row r="189" spans="15:15">
       <c r="O189" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
     </row>
     <row r="190" spans="15:15">
       <c r="O190" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
     </row>
     <row r="191" spans="15:15">
       <c r="O191" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row r="192" spans="15:15">
       <c r="O192" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="193" spans="15:15">
       <c r="O193" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
     </row>
     <row r="194" spans="15:15">
       <c r="O194" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="195" spans="15:15">
       <c r="O195" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
     </row>
     <row r="196" spans="15:15">
       <c r="O196" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
     </row>
     <row r="197" spans="15:15">
       <c r="O197" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
     </row>
     <row r="198" spans="15:15">
       <c r="O198" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
     </row>
     <row r="199" spans="15:15">
       <c r="O199" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
     </row>
     <row r="200" spans="15:15">
       <c r="O200" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
     </row>
     <row r="201" spans="15:15">
       <c r="O201" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
     <row r="202" spans="15:15">
       <c r="O202" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="203" spans="15:15">
       <c r="O203" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
     </row>
     <row r="204" spans="15:15">
       <c r="O204" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="205" spans="15:15">
       <c r="O205" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
     </row>
     <row r="206" spans="15:15">
       <c r="O206" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
     </row>
     <row r="207" spans="15:15">
       <c r="O207" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
     </row>
     <row r="208" spans="15:15">
       <c r="O208" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="209" spans="15:15">
       <c r="O209" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
     </row>
     <row r="210" spans="15:15">
       <c r="O210" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
     </row>
     <row r="211" spans="15:15">
       <c r="O211" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
     </row>
     <row r="212" spans="15:15">
       <c r="O212" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="213" spans="15:15">
       <c r="O213" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
     </row>
     <row r="214" spans="15:15">
       <c r="O214" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
     </row>
     <row r="215" spans="15:15">
       <c r="O215" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
     </row>
     <row r="216" spans="15:15">
       <c r="O216" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
     </row>
     <row r="217" spans="15:15">
       <c r="O217" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
     <row r="218" spans="15:15">
       <c r="O218" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
     </row>
     <row r="219" spans="15:15">
       <c r="O219" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
     </row>
     <row r="220" spans="15:15">
       <c r="O220" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
     </row>
     <row r="221" spans="15:15">
       <c r="O221" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
     </row>
     <row r="222" spans="15:15">
       <c r="O222" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
     </row>
     <row r="223" spans="15:15">
       <c r="O223" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
     </row>
     <row r="224" spans="15:15">
       <c r="O224" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="225" spans="15:15">
       <c r="O225" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
     </row>
     <row r="226" spans="15:15">
       <c r="O226" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
     </row>
     <row r="227" spans="15:15">
       <c r="O227" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
     </row>
     <row r="228" spans="15:15">
       <c r="O228" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
     </row>
     <row r="229" spans="15:15">
       <c r="O229" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
     </row>
     <row r="230" spans="15:15">
       <c r="O230" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
     </row>
     <row r="231" spans="15:15">
       <c r="O231" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
     </row>
     <row r="232" spans="15:15">
       <c r="O232" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
     </row>
     <row r="233" spans="15:15">
       <c r="O233" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
     </row>
     <row r="234" spans="15:15">
       <c r="O234" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
     </row>
     <row r="235" spans="15:15">
       <c r="O235" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
     </row>
     <row r="236" spans="15:15">
       <c r="O236" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
     </row>
     <row r="237" spans="15:15">
       <c r="O237" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
     </row>
     <row r="238" spans="15:15">
       <c r="O238" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
     </row>
     <row r="239" spans="15:15">
       <c r="O239" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
     </row>
     <row r="240" spans="15:15">
       <c r="O240" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
     </row>
     <row r="241" spans="15:15">
       <c r="O241" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
     </row>
     <row r="242" spans="15:15">
       <c r="O242" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
     </row>
     <row r="243" spans="15:15">
       <c r="O243" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
     </row>
     <row r="244" spans="15:15">
       <c r="O244" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
     </row>
     <row r="245" spans="15:15">
       <c r="O245" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
     </row>
     <row r="246" spans="15:15">
       <c r="O246" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
     </row>
     <row r="247" spans="15:15">
       <c r="O247" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
     </row>
     <row r="248" spans="15:15">
       <c r="O248" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
     </row>
     <row r="249" spans="15:15">
       <c r="O249" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
     </row>
     <row r="250" spans="15:15">
       <c r="O250" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
     </row>
     <row r="251" spans="15:15">
       <c r="O251" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
     </row>
     <row r="252" spans="15:15">
       <c r="O252" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
     </row>
     <row r="253" spans="15:15">
       <c r="O253" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
     </row>
     <row r="254" spans="15:15">
       <c r="O254" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
     </row>
     <row r="255" spans="15:15">
       <c r="O255" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
     </row>
     <row r="256" spans="15:15">
       <c r="O256" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="257" spans="15:15">
       <c r="O257" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
     </row>
     <row r="258" spans="15:15">
       <c r="O258" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
     </row>
     <row r="259" spans="15:15">
       <c r="O259" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
     </row>
     <row r="260" spans="15:15">
       <c r="O260" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
     </row>
     <row r="261" spans="15:15">
       <c r="O261" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
     </row>
     <row r="262" spans="15:15">
       <c r="O262" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
     </row>
     <row r="263" spans="15:15">
       <c r="O263" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
     </row>
     <row r="264" spans="15:15">
       <c r="O264" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
     </row>
     <row r="265" spans="15:15">
       <c r="O265" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
     </row>
     <row r="266" spans="15:15">
       <c r="O266" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
     </row>
     <row r="267" spans="15:15">
       <c r="O267" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
     </row>
     <row r="268" spans="15:15">
       <c r="O268" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
     </row>
     <row r="269" spans="15:15">
       <c r="O269" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
     </row>
     <row r="270" spans="15:15">
       <c r="O270" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
     </row>
     <row r="271" spans="15:15">
       <c r="O271" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
     </row>
     <row r="272" spans="15:15">
       <c r="O272" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
     </row>
     <row r="273" spans="15:15">
       <c r="O273" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
     </row>
     <row r="274" spans="15:15">
       <c r="O274" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
     </row>
     <row r="275" spans="15:15">
       <c r="O275" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
     </row>
     <row r="276" spans="15:15">
       <c r="O276" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
     </row>
     <row r="277" spans="15:15">
       <c r="O277" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
     </row>
     <row r="278" spans="15:15">
       <c r="O278" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
     </row>
     <row r="279" spans="15:15">
       <c r="O279" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
     </row>
     <row r="280" spans="15:15">
       <c r="O280" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
     </row>
     <row r="281" spans="15:15">
       <c r="O281" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
     </row>
     <row r="282" spans="15:15">
       <c r="O282" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
     </row>
     <row r="283" spans="15:15">
       <c r="O283" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
     </row>
     <row r="284" spans="15:15">
       <c r="O284" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
     </row>
     <row r="285" spans="15:15">
       <c r="O285" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
     </row>
     <row r="286" spans="15:15">
       <c r="O286" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
     </row>
     <row r="287" spans="15:15">
       <c r="O287" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
     </row>
     <row r="288" spans="15:15">
       <c r="O288" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
     </row>
     <row r="289" spans="15:15">
       <c r="O289" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
     </row>
   </sheetData>

--- a/templates/ERC000043/metadata_template_ERC000043.xlsx
+++ b/templates/ERC000043/metadata_template_ERC000043.xlsx
@@ -18,8 +18,8 @@
   </sheets>
   <definedNames>
     <definedName name="fileformat">'cv_run'!$D$1:$D$24</definedName>
-    <definedName name="geographiclocationcountryandorsea">'cv_sample'!$O$1:$O$289</definedName>
-    <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$86</definedName>
+    <definedName name="geographiclocationcountryandorsea">'cv_sample'!$O$1:$O$294</definedName>
+    <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$87</definedName>
     <definedName name="libraryselection">'cv_experiment'!$I$1:$I$31</definedName>
     <definedName name="librarysource">'cv_experiment'!$H$1:$H$9</definedName>
     <definedName name="librarystrategy">'cv_experiment'!$G$1:$G$41</definedName>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="606" uniqueCount="598">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="612" uniqueCount="604">
   <si>
     <t>alias</t>
   </si>
@@ -555,6 +555,9 @@
     <t>DNBSEQ-G50</t>
   </si>
   <si>
+    <t>DNBSEQ-G800</t>
+  </si>
+  <si>
     <t>DNBSEQ-T10x4RS</t>
   </si>
   <si>
@@ -840,19 +843,19 @@
     <t>(Optional) Free-form text describing the sample, its origin, and its method of isolation.</t>
   </si>
   <si>
-    <t>sample collection method</t>
+    <t>sample_collection_method</t>
   </si>
   <si>
     <t>(Optional) The method employed for collecting the sample. can be provided in the form of a pmid, doi, url or text.</t>
   </si>
   <si>
-    <t>sample storage conditions</t>
+    <t>sample_storage_conditions</t>
   </si>
   <si>
     <t>(Optional) Conditions at which sample was stored, usually storage temperature, duration and location. in soil context: explain how and for how long the soil sample was stored before dna extraction (fresh/frozen/other).</t>
   </si>
   <si>
-    <t>sample storage temperature</t>
+    <t>sample_storage_temperature</t>
   </si>
   <si>
     <t>(Optional) Temperature at which sample was stored, e.g. -80 (Units: °C)</t>
@@ -864,37 +867,37 @@
     <t>(Recommended) Name of persons or institute who collected the specimen</t>
   </si>
   <si>
-    <t>collection date</t>
+    <t>collection_date</t>
   </si>
   <si>
     <t>(Mandatory) The date the sample was collected with the intention of sequencing, either as an instance (single point in time) or interval. in case no exact time is available, the date/time can be right truncated i.e. all of these are valid iso8601 compliant times: 2008-01-23t19:23:10+00:00; 2008-01-23t19:23:10; 2008-01-23; 2008-01; 2008.</t>
   </si>
   <si>
-    <t>geographic location (latitude)</t>
+    <t>geographic_location_latitude</t>
   </si>
   <si>
     <t>(Recommended) The geographical origin of the sample as defined by latitude. the values should be reported in decimal degrees and in wgs84 system (Units: DD)</t>
   </si>
   <si>
-    <t>geographic location (longitude)</t>
+    <t>geographic_location_longitude</t>
   </si>
   <si>
     <t>(Recommended) The geographical origin of the sample as defined by longitude. the values should be reported in decimal degrees and in wgs84 system (Units: DD)</t>
   </si>
   <si>
-    <t>amount or size of sample collected</t>
-  </si>
-  <si>
-    <t>(Optional) The total amount or size (volume (ml), mass (g) or area (m2) ) of sample collected. (Units: m3)</t>
-  </si>
-  <si>
-    <t>water temperature</t>
+    <t>amount_or_size_of_sample_collected</t>
+  </si>
+  <si>
+    <t>(Optional) The total amount or size (volume (ml), mass (g) or area (m2) ) of sample collected. (Units: kg)</t>
+  </si>
+  <si>
+    <t>water_temperature</t>
   </si>
   <si>
     <t>(Optional) Temperature of water at the time of taking the sample. format: ##.####, sdn:p02:75:temp, sdn:p06:46:upaa for °c. example: 17.7122. (Units: ºC)</t>
   </si>
   <si>
-    <t>sample storage duration</t>
+    <t>sample_storage_duration</t>
   </si>
   <si>
     <t>(Optional) Duration for which the sample was stored. indicate the duration for which the sample was stored written in iso 8601 format.</t>
@@ -1113,9 +1116,6 @@
     <t>Dominican Republic</t>
   </si>
   <si>
-    <t>East Timor</t>
-  </si>
-  <si>
     <t>Ecuador</t>
   </si>
   <si>
@@ -1134,6 +1134,9 @@
     <t>Estonia</t>
   </si>
   <si>
+    <t>Eswatini</t>
+  </si>
+  <si>
     <t>Ethiopia</t>
   </si>
   <si>
@@ -1335,6 +1338,9 @@
     <t>Liechtenstein</t>
   </si>
   <si>
+    <t>Line Islands</t>
+  </si>
+  <si>
     <t>Lithuania</t>
   </si>
   <si>
@@ -1344,9 +1350,6 @@
     <t>Macau</t>
   </si>
   <si>
-    <t>Macedonia</t>
-  </si>
-  <si>
     <t>Madagascar</t>
   </si>
   <si>
@@ -1386,7 +1389,7 @@
     <t>Mexico</t>
   </si>
   <si>
-    <t>Micronesia</t>
+    <t>Micronesia, Federated States of</t>
   </si>
   <si>
     <t>Midway Islands</t>
@@ -1455,6 +1458,9 @@
     <t>North Korea</t>
   </si>
   <si>
+    <t>North Macedonia</t>
+  </si>
+  <si>
     <t>North Sea</t>
   </si>
   <si>
@@ -1530,6 +1536,9 @@
     <t>Rwanda</t>
   </si>
   <si>
+    <t>Saint Barthelemy</t>
+  </si>
+  <si>
     <t>Saint Helena</t>
   </si>
   <si>
@@ -1551,6 +1560,9 @@
     <t>San Marino</t>
   </si>
   <si>
+    <t>Saint Martin</t>
+  </si>
+  <si>
     <t>Sao Tome and Principe</t>
   </si>
   <si>
@@ -1596,6 +1608,9 @@
     <t>South Korea</t>
   </si>
   <si>
+    <t>South Sudan</t>
+  </si>
+  <si>
     <t>Southern Ocean</t>
   </si>
   <si>
@@ -1608,6 +1623,9 @@
     <t>Sri Lanka</t>
   </si>
   <si>
+    <t>State of Palestine</t>
+  </si>
+  <si>
     <t>Sudan</t>
   </si>
   <si>
@@ -1617,9 +1635,6 @@
     <t>Svalbard</t>
   </si>
   <si>
-    <t>Swaziland</t>
-  </si>
-  <si>
     <t>Sweden</t>
   </si>
   <si>
@@ -1644,6 +1659,9 @@
     <t>Thailand</t>
   </si>
   <si>
+    <t>Timor-Leste</t>
+  </si>
+  <si>
     <t>Togo</t>
   </si>
   <si>
@@ -1704,12 +1722,12 @@
     <t>Viet Nam</t>
   </si>
   <si>
+    <t>Wake Island</t>
+  </si>
+  <si>
     <t>Virgin Islands</t>
   </si>
   <si>
-    <t>Wake Island</t>
-  </si>
-  <si>
     <t>Wallis and Futuna</t>
   </si>
   <si>
@@ -1767,19 +1785,19 @@
     <t>restricted access</t>
   </si>
   <si>
-    <t>geographic location (country and/or sea)</t>
+    <t>geographic_location_country_andor_sea</t>
   </si>
   <si>
     <t>(Mandatory) The geographical origin of where the sample was collected from, with the intention of sequencing, as defined by the country or sea name. country or sea names should be chosen from the insdc country list (http://insdc.org/country.html).</t>
   </si>
   <si>
-    <t>light intensity</t>
+    <t>light_intensity</t>
   </si>
   <si>
     <t>(Optional) Measurement of light intensity (Units: lux)</t>
   </si>
   <si>
-    <t>pH</t>
+    <t>ph</t>
   </si>
   <si>
     <t>(Optional) Ph measurement</t>
@@ -1803,13 +1821,13 @@
     <t>(Mandatory) Name of the strain from which the sample was obtained.</t>
   </si>
   <si>
-    <t>Further Details</t>
+    <t>further_details</t>
   </si>
   <si>
     <t>(Optional) Reference details related to a sample in form of an uri.</t>
   </si>
   <si>
-    <t>isolation and growth condition</t>
+    <t>isolation_and_growth_condition</t>
   </si>
   <si>
     <t>(Optional) Publication reference in the form of pubmed id (pmid), digital object identifier (doi) or url for isolation and growth condition specifications of the organism/material. mandatory for migs and mimarks specimen.</t>
@@ -1818,10 +1836,10 @@
     <t>depth</t>
   </si>
   <si>
-    <t>(Recommended) The vertical distance below local surface, e.g. for sediment or soil samples depth is measured from sediment or soil surface, respectively. depth can be reported as an interval for subsurface samples. (Units: mm)</t>
-  </si>
-  <si>
-    <t>growth condition</t>
+    <t>(Recommended) The vertical distance below local surface, e.g. for sediment or soil samples depth is measured from sediment or soil surface, respectively. depth can be reported as an interval for subsurface samples. (Units: m)</t>
+  </si>
+  <si>
+    <t>growth_condition</t>
   </si>
   <si>
     <t>(Optional) A role that a material entity can play which enables particular conditions used to grow organisms or parts of the organism. this includes isolated environments such as cultures and open environments such as field studies.</t>
@@ -2354,7 +2372,7 @@
         <v>143</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="150" customHeight="1">
@@ -2398,7 +2416,7 @@
         <v>144</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
   </sheetData>
@@ -2425,7 +2443,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="G1:N86"/>
+  <dimension ref="G1:N87"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="7:14">
@@ -3149,6 +3167,11 @@
     </row>
     <row r="86" spans="14:14">
       <c r="N86" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="87" spans="14:14">
+      <c r="N87" t="s">
         <v>117</v>
       </c>
     </row>
@@ -3170,27 +3193,27 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
   </sheetData>
@@ -3210,122 +3233,122 @@
   <sheetData>
     <row r="1" spans="4:4">
       <c r="D1" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="2" spans="4:4">
       <c r="D2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="3" spans="4:4">
       <c r="D3" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="4" spans="4:4">
       <c r="D4" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="5" spans="4:4">
       <c r="D5" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="6" spans="4:4">
       <c r="D6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="7" spans="4:4">
       <c r="D7" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="8" spans="4:4">
       <c r="D8" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="9" spans="4:4">
       <c r="D9" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="10" spans="4:4">
       <c r="D10" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="11" spans="4:4">
       <c r="D11" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="12" spans="4:4">
       <c r="D12" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="13" spans="4:4">
       <c r="D13" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="14" spans="4:4">
       <c r="D14" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="15" spans="4:4">
       <c r="D15" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="16" spans="4:4">
       <c r="D16" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="17" spans="4:4">
       <c r="D17" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="18" spans="4:4">
       <c r="D18" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="19" spans="4:4">
       <c r="D19" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="20" spans="4:4">
       <c r="D20" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="21" spans="4:4">
       <c r="D21" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="22" spans="4:4">
       <c r="D22" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="23" spans="4:4">
       <c r="D23" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="24" spans="4:4">
       <c r="D24" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
   </sheetData>
@@ -3349,144 +3372,144 @@
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>578</v>
+        <v>584</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>580</v>
+        <v>586</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>582</v>
+        <v>588</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>584</v>
+        <v>590</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>586</v>
+        <v>592</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>588</v>
+        <v>594</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>590</v>
+        <v>596</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>592</v>
+        <v>598</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>594</v>
+        <v>600</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>596</v>
+        <v>602</v>
       </c>
     </row>
     <row r="2" spans="1:24" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>579</v>
+        <v>585</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>581</v>
+        <v>587</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>583</v>
+        <v>589</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>585</v>
+        <v>591</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>587</v>
+        <v>593</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>589</v>
+        <v>595</v>
       </c>
       <c r="U2" s="2" t="s">
-        <v>591</v>
+        <v>597</v>
       </c>
       <c r="V2" s="2" t="s">
-        <v>593</v>
+        <v>599</v>
       </c>
       <c r="W2" s="2" t="s">
-        <v>595</v>
+        <v>601</v>
       </c>
       <c r="X2" s="2" t="s">
-        <v>597</v>
+        <v>603</v>
       </c>
     </row>
   </sheetData>
@@ -3501,1452 +3524,1477 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="O1:O289"/>
+  <dimension ref="O1:O294"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="15:15">
       <c r="O1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="2" spans="15:15">
       <c r="O2" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="3" spans="15:15">
       <c r="O3" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="4" spans="15:15">
       <c r="O4" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="5" spans="15:15">
       <c r="O5" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="6" spans="15:15">
       <c r="O6" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="7" spans="15:15">
       <c r="O7" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="8" spans="15:15">
       <c r="O8" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="9" spans="15:15">
       <c r="O9" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="10" spans="15:15">
       <c r="O10" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="11" spans="15:15">
       <c r="O11" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="12" spans="15:15">
       <c r="O12" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="13" spans="15:15">
       <c r="O13" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="14" spans="15:15">
       <c r="O14" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="15" spans="15:15">
       <c r="O15" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="16" spans="15:15">
       <c r="O16" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="17" spans="15:15">
       <c r="O17" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="18" spans="15:15">
       <c r="O18" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="19" spans="15:15">
       <c r="O19" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="20" spans="15:15">
       <c r="O20" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="21" spans="15:15">
       <c r="O21" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="22" spans="15:15">
       <c r="O22" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="23" spans="15:15">
       <c r="O23" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="24" spans="15:15">
       <c r="O24" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="25" spans="15:15">
       <c r="O25" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="26" spans="15:15">
       <c r="O26" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="27" spans="15:15">
       <c r="O27" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="28" spans="15:15">
       <c r="O28" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="29" spans="15:15">
       <c r="O29" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="30" spans="15:15">
       <c r="O30" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="31" spans="15:15">
       <c r="O31" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="32" spans="15:15">
       <c r="O32" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="33" spans="15:15">
       <c r="O33" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="34" spans="15:15">
       <c r="O34" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="35" spans="15:15">
       <c r="O35" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="36" spans="15:15">
       <c r="O36" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="37" spans="15:15">
       <c r="O37" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="38" spans="15:15">
       <c r="O38" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="39" spans="15:15">
       <c r="O39" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="40" spans="15:15">
       <c r="O40" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="41" spans="15:15">
       <c r="O41" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="42" spans="15:15">
       <c r="O42" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="43" spans="15:15">
       <c r="O43" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="44" spans="15:15">
       <c r="O44" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="45" spans="15:15">
       <c r="O45" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="46" spans="15:15">
       <c r="O46" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="47" spans="15:15">
       <c r="O47" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="48" spans="15:15">
       <c r="O48" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="49" spans="15:15">
       <c r="O49" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="50" spans="15:15">
       <c r="O50" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="51" spans="15:15">
       <c r="O51" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="52" spans="15:15">
       <c r="O52" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="53" spans="15:15">
       <c r="O53" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="54" spans="15:15">
       <c r="O54" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="55" spans="15:15">
       <c r="O55" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="56" spans="15:15">
       <c r="O56" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="57" spans="15:15">
       <c r="O57" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="58" spans="15:15">
       <c r="O58" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="59" spans="15:15">
       <c r="O59" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="60" spans="15:15">
       <c r="O60" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="61" spans="15:15">
       <c r="O61" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="62" spans="15:15">
       <c r="O62" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="63" spans="15:15">
       <c r="O63" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="64" spans="15:15">
       <c r="O64" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="65" spans="15:15">
       <c r="O65" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="66" spans="15:15">
       <c r="O66" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="67" spans="15:15">
       <c r="O67" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="68" spans="15:15">
       <c r="O68" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="69" spans="15:15">
       <c r="O69" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="70" spans="15:15">
       <c r="O70" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="71" spans="15:15">
       <c r="O71" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="72" spans="15:15">
       <c r="O72" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="73" spans="15:15">
       <c r="O73" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="74" spans="15:15">
       <c r="O74" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="75" spans="15:15">
       <c r="O75" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="76" spans="15:15">
       <c r="O76" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="77" spans="15:15">
       <c r="O77" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="78" spans="15:15">
       <c r="O78" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="79" spans="15:15">
       <c r="O79" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="80" spans="15:15">
       <c r="O80" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="81" spans="15:15">
       <c r="O81" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="82" spans="15:15">
       <c r="O82" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="83" spans="15:15">
       <c r="O83" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="84" spans="15:15">
       <c r="O84" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="85" spans="15:15">
       <c r="O85" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="86" spans="15:15">
       <c r="O86" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="87" spans="15:15">
       <c r="O87" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="88" spans="15:15">
       <c r="O88" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="89" spans="15:15">
       <c r="O89" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="90" spans="15:15">
       <c r="O90" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="91" spans="15:15">
       <c r="O91" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="92" spans="15:15">
       <c r="O92" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="93" spans="15:15">
       <c r="O93" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="94" spans="15:15">
       <c r="O94" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="95" spans="15:15">
       <c r="O95" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="96" spans="15:15">
       <c r="O96" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="97" spans="15:15">
       <c r="O97" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="98" spans="15:15">
       <c r="O98" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="99" spans="15:15">
       <c r="O99" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="100" spans="15:15">
       <c r="O100" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="101" spans="15:15">
       <c r="O101" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="102" spans="15:15">
       <c r="O102" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="103" spans="15:15">
       <c r="O103" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="104" spans="15:15">
       <c r="O104" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="105" spans="15:15">
       <c r="O105" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="106" spans="15:15">
       <c r="O106" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="107" spans="15:15">
       <c r="O107" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="108" spans="15:15">
       <c r="O108" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="109" spans="15:15">
       <c r="O109" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="110" spans="15:15">
       <c r="O110" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="111" spans="15:15">
       <c r="O111" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="112" spans="15:15">
       <c r="O112" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="113" spans="15:15">
       <c r="O113" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="114" spans="15:15">
       <c r="O114" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="115" spans="15:15">
       <c r="O115" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="116" spans="15:15">
       <c r="O116" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="117" spans="15:15">
       <c r="O117" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="118" spans="15:15">
       <c r="O118" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="119" spans="15:15">
       <c r="O119" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="120" spans="15:15">
       <c r="O120" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="121" spans="15:15">
       <c r="O121" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="122" spans="15:15">
       <c r="O122" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="123" spans="15:15">
       <c r="O123" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="124" spans="15:15">
       <c r="O124" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="125" spans="15:15">
       <c r="O125" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="126" spans="15:15">
       <c r="O126" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="127" spans="15:15">
       <c r="O127" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="128" spans="15:15">
       <c r="O128" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="129" spans="15:15">
       <c r="O129" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="130" spans="15:15">
       <c r="O130" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="131" spans="15:15">
       <c r="O131" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="132" spans="15:15">
       <c r="O132" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="133" spans="15:15">
       <c r="O133" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="134" spans="15:15">
       <c r="O134" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="135" spans="15:15">
       <c r="O135" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="136" spans="15:15">
       <c r="O136" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="137" spans="15:15">
       <c r="O137" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="138" spans="15:15">
       <c r="O138" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="139" spans="15:15">
       <c r="O139" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="140" spans="15:15">
       <c r="O140" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="141" spans="15:15">
       <c r="O141" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="142" spans="15:15">
       <c r="O142" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="143" spans="15:15">
       <c r="O143" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="144" spans="15:15">
       <c r="O144" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="145" spans="15:15">
       <c r="O145" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="146" spans="15:15">
       <c r="O146" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="147" spans="15:15">
       <c r="O147" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="148" spans="15:15">
       <c r="O148" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="149" spans="15:15">
       <c r="O149" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="150" spans="15:15">
       <c r="O150" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="151" spans="15:15">
       <c r="O151" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="152" spans="15:15">
       <c r="O152" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="153" spans="15:15">
       <c r="O153" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="154" spans="15:15">
       <c r="O154" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="155" spans="15:15">
       <c r="O155" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="156" spans="15:15">
       <c r="O156" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="157" spans="15:15">
       <c r="O157" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="158" spans="15:15">
       <c r="O158" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="159" spans="15:15">
       <c r="O159" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="160" spans="15:15">
       <c r="O160" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="161" spans="15:15">
       <c r="O161" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="162" spans="15:15">
       <c r="O162" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="163" spans="15:15">
       <c r="O163" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="164" spans="15:15">
       <c r="O164" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="165" spans="15:15">
       <c r="O165" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="166" spans="15:15">
       <c r="O166" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="167" spans="15:15">
       <c r="O167" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="168" spans="15:15">
       <c r="O168" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="169" spans="15:15">
       <c r="O169" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="170" spans="15:15">
       <c r="O170" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="171" spans="15:15">
       <c r="O171" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="172" spans="15:15">
       <c r="O172" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="173" spans="15:15">
       <c r="O173" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="174" spans="15:15">
       <c r="O174" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="175" spans="15:15">
       <c r="O175" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="176" spans="15:15">
       <c r="O176" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="177" spans="15:15">
       <c r="O177" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="178" spans="15:15">
       <c r="O178" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="179" spans="15:15">
       <c r="O179" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="180" spans="15:15">
       <c r="O180" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="181" spans="15:15">
       <c r="O181" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="182" spans="15:15">
       <c r="O182" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="183" spans="15:15">
       <c r="O183" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="184" spans="15:15">
       <c r="O184" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="185" spans="15:15">
       <c r="O185" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="186" spans="15:15">
       <c r="O186" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="187" spans="15:15">
       <c r="O187" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="188" spans="15:15">
       <c r="O188" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="189" spans="15:15">
       <c r="O189" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="190" spans="15:15">
       <c r="O190" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="191" spans="15:15">
       <c r="O191" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="192" spans="15:15">
       <c r="O192" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="193" spans="15:15">
       <c r="O193" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="194" spans="15:15">
       <c r="O194" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="195" spans="15:15">
       <c r="O195" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="196" spans="15:15">
       <c r="O196" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="197" spans="15:15">
       <c r="O197" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="198" spans="15:15">
       <c r="O198" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="199" spans="15:15">
       <c r="O199" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="200" spans="15:15">
       <c r="O200" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="201" spans="15:15">
       <c r="O201" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="202" spans="15:15">
       <c r="O202" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="203" spans="15:15">
       <c r="O203" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="204" spans="15:15">
       <c r="O204" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="205" spans="15:15">
       <c r="O205" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="206" spans="15:15">
       <c r="O206" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="207" spans="15:15">
       <c r="O207" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="208" spans="15:15">
       <c r="O208" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="209" spans="15:15">
       <c r="O209" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="210" spans="15:15">
       <c r="O210" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="211" spans="15:15">
       <c r="O211" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="212" spans="15:15">
       <c r="O212" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="213" spans="15:15">
       <c r="O213" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="214" spans="15:15">
       <c r="O214" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="215" spans="15:15">
       <c r="O215" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="216" spans="15:15">
       <c r="O216" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
     </row>
     <row r="217" spans="15:15">
       <c r="O217" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="218" spans="15:15">
       <c r="O218" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="219" spans="15:15">
       <c r="O219" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="220" spans="15:15">
       <c r="O220" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="221" spans="15:15">
       <c r="O221" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="222" spans="15:15">
       <c r="O222" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="223" spans="15:15">
       <c r="O223" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="224" spans="15:15">
       <c r="O224" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="225" spans="15:15">
       <c r="O225" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="226" spans="15:15">
       <c r="O226" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="227" spans="15:15">
       <c r="O227" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="228" spans="15:15">
       <c r="O228" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="229" spans="15:15">
       <c r="O229" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="230" spans="15:15">
       <c r="O230" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
     <row r="231" spans="15:15">
       <c r="O231" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="232" spans="15:15">
       <c r="O232" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="233" spans="15:15">
       <c r="O233" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
     </row>
     <row r="234" spans="15:15">
       <c r="O234" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="235" spans="15:15">
       <c r="O235" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
     </row>
     <row r="236" spans="15:15">
       <c r="O236" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
     </row>
     <row r="237" spans="15:15">
       <c r="O237" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
     </row>
     <row r="238" spans="15:15">
       <c r="O238" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="239" spans="15:15">
       <c r="O239" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="240" spans="15:15">
       <c r="O240" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
     </row>
     <row r="241" spans="15:15">
       <c r="O241" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="242" spans="15:15">
       <c r="O242" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
     </row>
     <row r="243" spans="15:15">
       <c r="O243" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
     </row>
     <row r="244" spans="15:15">
       <c r="O244" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
     </row>
     <row r="245" spans="15:15">
       <c r="O245" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="246" spans="15:15">
       <c r="O246" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="247" spans="15:15">
       <c r="O247" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
     </row>
     <row r="248" spans="15:15">
       <c r="O248" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="249" spans="15:15">
       <c r="O249" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
     </row>
     <row r="250" spans="15:15">
       <c r="O250" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="251" spans="15:15">
       <c r="O251" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
     </row>
     <row r="252" spans="15:15">
       <c r="O252" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
     </row>
     <row r="253" spans="15:15">
       <c r="O253" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
     </row>
     <row r="254" spans="15:15">
       <c r="O254" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
     </row>
     <row r="255" spans="15:15">
       <c r="O255" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
     </row>
     <row r="256" spans="15:15">
       <c r="O256" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
     </row>
     <row r="257" spans="15:15">
       <c r="O257" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
     <row r="258" spans="15:15">
       <c r="O258" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="259" spans="15:15">
       <c r="O259" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
     </row>
     <row r="260" spans="15:15">
       <c r="O260" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
     </row>
     <row r="261" spans="15:15">
       <c r="O261" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
     </row>
     <row r="262" spans="15:15">
       <c r="O262" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
     </row>
     <row r="263" spans="15:15">
       <c r="O263" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
     </row>
     <row r="264" spans="15:15">
       <c r="O264" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
     </row>
     <row r="265" spans="15:15">
       <c r="O265" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
     </row>
     <row r="266" spans="15:15">
       <c r="O266" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
     </row>
     <row r="267" spans="15:15">
       <c r="O267" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
     </row>
     <row r="268" spans="15:15">
       <c r="O268" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
     </row>
     <row r="269" spans="15:15">
       <c r="O269" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="270" spans="15:15">
       <c r="O270" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
     </row>
     <row r="271" spans="15:15">
       <c r="O271" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
     <row r="272" spans="15:15">
       <c r="O272" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="273" spans="15:15">
       <c r="O273" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
     </row>
     <row r="274" spans="15:15">
       <c r="O274" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
     </row>
     <row r="275" spans="15:15">
       <c r="O275" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
     </row>
     <row r="276" spans="15:15">
       <c r="O276" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
     </row>
     <row r="277" spans="15:15">
       <c r="O277" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
     <row r="278" spans="15:15">
       <c r="O278" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
     </row>
     <row r="279" spans="15:15">
       <c r="O279" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
     </row>
     <row r="280" spans="15:15">
       <c r="O280" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
     </row>
     <row r="281" spans="15:15">
       <c r="O281" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
     </row>
     <row r="282" spans="15:15">
       <c r="O282" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
     </row>
     <row r="283" spans="15:15">
       <c r="O283" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
     </row>
     <row r="284" spans="15:15">
       <c r="O284" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
     </row>
     <row r="285" spans="15:15">
       <c r="O285" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
     </row>
     <row r="286" spans="15:15">
       <c r="O286" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="287" spans="15:15">
       <c r="O287" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
     </row>
     <row r="288" spans="15:15">
       <c r="O288" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
     </row>
     <row r="289" spans="15:15">
       <c r="O289" t="s">
-        <v>577</v>
+        <v>578</v>
+      </c>
+    </row>
+    <row r="290" spans="15:15">
+      <c r="O290" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="291" spans="15:15">
+      <c r="O291" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="292" spans="15:15">
+      <c r="O292" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="293" spans="15:15">
+      <c r="O293" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="294" spans="15:15">
+      <c r="O294" t="s">
+        <v>583</v>
       </c>
     </row>
   </sheetData>

--- a/templates/ERC000043/metadata_template_ERC000043.xlsx
+++ b/templates/ERC000043/metadata_template_ERC000043.xlsx
@@ -906,7 +906,7 @@
     <t>amount or size of sample collected</t>
   </si>
   <si>
-    <t>(Optional) The total amount or size (volume (ml), mass (g) or area (m2) ) of sample collected. (Units: m3)</t>
+    <t>(Optional) The total amount or size (volume (ml), mass (g) or area (m2) ) of sample collected. (Units: kg)</t>
   </si>
   <si>
     <t>water temperature</t>
@@ -1854,7 +1854,7 @@
     <t>depth</t>
   </si>
   <si>
-    <t>(Recommended) The vertical distance below local surface, e.g. for sediment or soil samples depth is measured from sediment or soil surface, respectively. depth can be reported as an interval for subsurface samples. (Units: mm)</t>
+    <t>(Recommended) The vertical distance below local surface, e.g. for sediment or soil samples depth is measured from sediment or soil surface, respectively. depth can be reported as an interval for subsurface samples. (Units: m)</t>
   </si>
   <si>
     <t>growth condition</t>
